--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_21_8.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_21_8.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_24</t>
+          <t>model_21_8_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9761846752092798</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7025324610829884</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9118546861089221</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9353243772162954</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9343185033597159</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1592531865350334</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H2" t="n">
-        <v>1.989166802450128</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2567542968827065</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7372674052518549</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4970108510672807</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3676403919067176</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3990653913020188</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N2" t="n">
-        <v>1.013292274301797</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4160544311889885</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P2" t="n">
-        <v>137.6745199501818</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q2" t="n">
-        <v>219.3392002163513</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_23</t>
+          <t>model_21_8_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9764590052177293</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7025251479613186</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9129431507103831</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9360789959432273</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9350964063390573</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1574187405053583</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H3" t="n">
-        <v>1.989215705328408</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2535837600601231</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J3" t="n">
-        <v>0.728665156571232</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4911244714689641</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3683641365331084</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3967603061110804</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N3" t="n">
-        <v>1.013139159878477</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4136512137492878</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P3" t="n">
-        <v>137.6976917743103</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q3" t="n">
-        <v>219.3623720404797</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_22</t>
+          <t>model_21_8_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9767618574919273</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7025152846514795</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9141455284314</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9369154095578136</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9359578458205881</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G4" t="n">
-        <v>0.155393565953289</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H4" t="n">
-        <v>1.989281661326718</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I4" t="n">
-        <v>0.250081411123813</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7191304900492623</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4846059724736786</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3691711086029488</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3941999060797567</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N4" t="n">
-        <v>1.012970126051017</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4109818121878719</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P4" t="n">
-        <v>137.7235884900754</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q4" t="n">
-        <v>219.3882687562449</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_21</t>
+          <t>model_21_8_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9770960101083896</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7025021488463321</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9154732781620092</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9378423616673756</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9369116167804844</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1531590858683747</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H5" t="n">
-        <v>1.989369500516223</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I5" t="n">
-        <v>0.246213872017423</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J5" t="n">
-        <v>0.708563733252887</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K5" t="n">
-        <v>0.477388802635155</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3700722679413886</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3913554469639776</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N5" t="n">
-        <v>1.012783622265085</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O5" t="n">
-        <v>0.408016258558692</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P5" t="n">
-        <v>137.7525562417316</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q5" t="n">
-        <v>219.4172365079011</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_20</t>
+          <t>model_21_8_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9774643224309492</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7024847880264831</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D6" t="n">
-        <v>0.916938081255232</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E6" t="n">
-        <v>0.938869181466283</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9379669896350354</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1506961796714968</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H6" t="n">
-        <v>1.989485592398493</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2419471166827402</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6968585383708306</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4694028128592769</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3710764335764725</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3881960582894897</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N6" t="n">
-        <v>1.012578052596679</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4047223681674949</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P6" t="n">
-        <v>137.7849790484503</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q6" t="n">
-        <v>219.4496593146197</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_19</t>
+          <t>model_21_8_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9778698227754886</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7024621476984212</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9185527824960639</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9400059475555481</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9391340228861209</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1479845970004041</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H7" t="n">
-        <v>1.989636988376493</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2372437301558318</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6839000147580975</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4605718906206678</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3722007507992336</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3846876616170632</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N7" t="n">
-        <v>1.012351726822983</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4010646117853409</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P7" t="n">
-        <v>137.8212941699115</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q7" t="n">
-        <v>219.4859744360809</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_18</t>
+          <t>model_21_8_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.978315688061157</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7024327688109848</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9203305969792213</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9412637495136165</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9404236290191971</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1450030937821186</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H8" t="n">
-        <v>1.989833445132057</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2320652188151721</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6695617471692867</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4508134613136738</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3734577687252368</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3807927176064671</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N8" t="n">
-        <v>1.012102871779819</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3970038519445681</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P8" t="n">
-        <v>137.8620004007215</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q8" t="n">
-        <v>219.526680666891</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_17</t>
+          <t>model_21_8_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9788052984382232</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7023948857281666</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9222862294300933</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9426546567305614</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9418477116456366</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1417290669362286</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H9" t="n">
-        <v>1.990086769481298</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2263687499648243</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6537061510320435</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4400374504984339</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3748640844108229</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M9" t="n">
-        <v>0.376469211139807</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N9" t="n">
-        <v>1.011829600871689</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3924962848567301</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P9" t="n">
-        <v>137.9076760464287</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q9" t="n">
-        <v>219.5723563125981</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_16</t>
+          <t>model_21_8_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9793419704330781</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7023462650544581</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9244348701095473</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9441912227299875</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9434186659528272</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1381403388354859</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H10" t="n">
-        <v>1.990411896150264</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2201100766156259</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J10" t="n">
-        <v>0.636190122911469</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K10" t="n">
-        <v>0.42815006398712</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3764389177205654</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3716723541447304</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N10" t="n">
-        <v>1.011530063014096</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3874952157285103</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P10" t="n">
-        <v>137.9589703249662</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q10" t="n">
-        <v>219.6236505911356</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_15</t>
+          <t>model_21_8_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.979929014082042</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7022840275471021</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9267918437483906</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9458869318184191</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9451495807688026</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1342147752517774</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H11" t="n">
-        <v>1.990828078648531</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2132445600873157</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6168599489466811</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4150522588240562</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3782015072887866</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3663533475372886</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N11" t="n">
-        <v>1.011202410744907</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O11" t="n">
-        <v>0.381949767997928</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P11" t="n">
-        <v>138.016627923517</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q11" t="n">
-        <v>219.6813081896864</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_14</t>
+          <t>model_21_8_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9805696703148384</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C12" t="n">
-        <v>0.702204706359892</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D12" t="n">
-        <v>0.929373816840284</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9477559056293912</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9470543158263781</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1299307040731166</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H12" t="n">
-        <v>1.991358499792646</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2057236533423658</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J12" t="n">
-        <v>0.59555465009077</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K12" t="n">
-        <v>0.400639158629219</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3801787553782141</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3604590185764765</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N12" t="n">
-        <v>1.010844835173113</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3758045052503111</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P12" t="n">
-        <v>138.0815080324745</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q12" t="n">
-        <v>219.746188298644</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_13</t>
+          <t>model_21_8_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9812667966050367</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7021037471577793</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9321961616180862</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9498127529921921</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9491468314651276</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1252690173605896</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H13" t="n">
-        <v>1.992033614442047</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1975025793340455</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5721076935265803</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3848051257328278</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3824034465537687</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3539336341188692</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N13" t="n">
-        <v>1.010455741429747</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3690013216669355</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P13" t="n">
-        <v>138.1545834306573</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q13" t="n">
-        <v>219.8192636968268</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="14">
@@ -1177,712 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9820227604312415</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C14" t="n">
-        <v>0.70197550425023</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9352745206366383</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E14" t="n">
-        <v>0.952072063849255</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9514411252292713</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1202138837738653</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H14" t="n">
-        <v>1.992891175355334</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1885357736075653</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5463527617369827</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3674442409381277</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3849023380604517</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M14" t="n">
-        <v>0.346718738711748</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N14" t="n">
-        <v>1.0100338081314</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3614792732254406</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P14" t="n">
-        <v>138.2369655158902</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q14" t="n">
-        <v>219.9016457820596</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_11</t>
+          <t>model_21_8_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9828390258634113</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7018128594420916</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9386239970034642</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9545476229028542</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9539504800040453</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1147555130703886</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H15" t="n">
-        <v>1.993978781936265</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1787792430385969</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5181327165106887</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3484559928616484</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3877128880195522</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3387558310500183</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N15" t="n">
-        <v>1.009578218122747</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O15" t="n">
-        <v>0.35317736809906</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P15" t="n">
-        <v>138.3299027740183</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q15" t="n">
-        <v>219.9945830401878</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_10</t>
+          <t>model_21_8_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9837157455547221</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7016067888998286</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D16" t="n">
-        <v>0.942257241260238</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9572519196786056</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9566867556742001</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1088928844576708</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H16" t="n">
-        <v>1.995356776601246</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1681961384653483</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4873051839555402</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3277506379421889</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L16" t="n">
-        <v>0.390883543684769</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M16" t="n">
-        <v>0.329989218699143</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N16" t="n">
-        <v>1.009088886202016</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3440375429110185</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P16" t="n">
-        <v>138.4347811826559</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q16" t="n">
-        <v>220.0994614488253</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_9</t>
+          <t>model_21_8_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9846513532575171</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7013458453041563</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9461844972013782</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9601953049750477</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9596597009106803</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1026364714410031</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H17" t="n">
-        <v>1.997101707627041</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1567566212257603</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4537521705207623</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K17" t="n">
-        <v>0.305254408140184</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3944659625481717</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3203692735594397</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N17" t="n">
-        <v>1.008566686553944</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3340080567906863</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P17" t="n">
-        <v>138.5531238745524</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q17" t="n">
-        <v>220.2178041407218</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_8</t>
+          <t>model_21_8_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9856413527763171</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7010155880510327</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9504112658013489</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9633830285726533</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9628743470505489</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G18" t="n">
-        <v>0.09601634010025828</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H18" t="n">
-        <v>1.999310139399373</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I18" t="n">
-        <v>0.144444667792678</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4174138315251458</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K18" t="n">
-        <v>0.280929231407285</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3985125309010306</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3098650352980444</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N18" t="n">
-        <v>1.008014128682986</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3230566313597326</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P18" t="n">
-        <v>138.6864737852412</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q18" t="n">
-        <v>220.3511540514106</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_7</t>
+          <t>model_21_8_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9866775972357444</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7005976717703328</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9549367957498467</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9668140376013588</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9663297457934703</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G19" t="n">
-        <v>0.08908696862860127</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H19" t="n">
-        <v>2.002104747492742</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1312624666221879</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3783021691226204</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2547822835172017</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L19" t="n">
-        <v>0.403100386602562</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2984744019653968</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N19" t="n">
-        <v>1.007435759682375</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3111810751842526</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P19" t="n">
-        <v>138.836284421546</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q19" t="n">
-        <v>220.5009646877155</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_6</t>
+          <t>model_21_8_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9877466750672352</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7000688566266077</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9597509368413857</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9704770727475369</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9700154549063639</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G20" t="n">
-        <v>0.08193804024677157</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H20" t="n">
-        <v>2.005640936793801</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1172395837655945</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3365455334486067</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2268925806832665</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4082994954015995</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2862482143992719</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N20" t="n">
-        <v>1.006839065078752</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2984343935017405</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P20" t="n">
-        <v>139.0035838481585</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q20" t="n">
-        <v>220.6682641143279</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_5</t>
+          <t>model_21_8_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9888279760212998</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6993996732636627</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9648297538939964</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9743463947920477</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9739074991170059</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G21" t="n">
-        <v>0.07470737578800875</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H21" t="n">
-        <v>2.01011576902312</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I21" t="n">
-        <v>0.102445738877251</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2924373377937984</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1974415434129576</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4142109363400504</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2733265003398111</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N21" t="n">
-        <v>1.006235548267181</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2849625753231328</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P21" t="n">
-        <v>139.1883529058449</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q21" t="n">
-        <v>220.8530331720143</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_4</t>
+          <t>model_21_8_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9898911282756276</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6985529119266638</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9701312663635094</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9783754446084513</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9779627170497117</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G22" t="n">
-        <v>0.06759807176795254</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H22" t="n">
-        <v>2.015778065982609</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0870032150896933</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2465083312235087</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K22" t="n">
-        <v>0.166755773156601</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4209355605272123</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2599962918350039</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N22" t="n">
-        <v>1.00564216096244</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2710648722449403</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P22" t="n">
-        <v>139.3883516409655</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q22" t="n">
-        <v>221.0530319071349</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_3</t>
+          <t>model_21_8_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9908929060213243</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6974817867108212</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9755852652292808</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9824904775498039</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9821120475732881</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G23" t="n">
-        <v>0.06089917936971648</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H23" t="n">
-        <v>2.022940685233027</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I23" t="n">
-        <v>0.07111652092339185</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1995991631534428</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K23" t="n">
-        <v>0.135357854406721</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4285934615147133</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2467775908985994</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N23" t="n">
-        <v>1.0050830291974</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2572834238431898</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P23" t="n">
-        <v>139.5970711588056</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q23" t="n">
-        <v>221.261751424975</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_2</t>
+          <t>model_21_8_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9917731085976255</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6961276868086124</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9810833258123229</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9865811768952623</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9862515274244998</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G24" t="n">
-        <v>0.05501326068903032</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H24" t="n">
-        <v>2.031995557514155</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I24" t="n">
-        <v>0.05510148147430781</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1529673850230981</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1040344755395471</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4373191596971022</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2345490581712711</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N24" t="n">
-        <v>1.00459175334086</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2445342971611067</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P24" t="n">
-        <v>139.800362038747</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q24" t="n">
-        <v>221.4650423049165</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_1</t>
+          <t>model_21_8_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9924502515809062</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6944183588080788</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9864610868129429</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9904927908799305</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9902329697318291</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G25" t="n">
-        <v>0.05048520244187533</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H25" t="n">
-        <v>2.043425841724454</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I25" t="n">
-        <v>0.03943685696320069</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1083770839375116</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K25" t="n">
-        <v>0.07390696427898205</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4472571166153908</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2246891239955226</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N25" t="n">
-        <v>1.004213813071122</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O25" t="n">
-        <v>0.234254605174619</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P25" t="n">
-        <v>139.9721500131856</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q25" t="n">
-        <v>221.6368302793551</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_21_8_0</t>
+          <t>model_21_8_24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9928168294155815</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6922661542020754</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9914735627111092</v>
+        <v>0.9984756130776821</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9940199661590224</v>
+        <v>0.99866309550685</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9938545245517844</v>
+        <v>0.9993799706599095</v>
       </c>
       <c r="G26" t="n">
-        <v>0.04803389477346607</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H26" t="n">
-        <v>2.05781764383479</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0248362540716444</v>
+        <v>0.0001319854125719838</v>
       </c>
       <c r="J26" t="n">
-        <v>0.06816917786784157</v>
+        <v>0.0005501763533926099</v>
       </c>
       <c r="K26" t="n">
-        <v>0.04650271596974299</v>
+        <v>0.0003410836791432291</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4585722057069202</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2191663632345668</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N26" t="n">
-        <v>1.004009211488978</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2284967290543785</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P26" t="n">
-        <v>140.0716967523214</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q26" t="n">
-        <v>221.7363770184908</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
   </sheetData>
